--- a/Data Appendix/CH_Hazard_Scoring.xlsx
+++ b/Data Appendix/CH_Hazard_Scoring.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Honours\Data Appendix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/48f02162ba686543/Other/Documents/GitHub/NVP_Honours_Data/Data Appendix/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{613B7D31-2787-43D0-B311-74209D39C33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{BE39197E-AE55-4011-B515-5F29F14891C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE39197E-AE55-4011-B515-5F29F14891C2}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="3" r:id="rId1"/>
@@ -2802,7 +2802,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2824,46 +2824,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="11" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="12" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="13" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="10" xfId="23" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="10" xfId="23" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="10" xfId="23" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="14" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="15" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="35" borderId="10" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2874,22 +2847,48 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="15" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="15" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="42" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="15" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="11" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="12" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="13" xfId="25" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="14" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="15" xfId="23" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -3268,362 +3267,361 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5130CB46-1631-441C-B066-5F119718A196}">
   <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.140625" customWidth="1"/>
-    <col min="2" max="2" width="46.28515625" customWidth="1"/>
-    <col min="5" max="5" width="43.140625" customWidth="1"/>
-    <col min="8" max="8" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.1796875" customWidth="1"/>
+    <col min="2" max="2" width="46.26953125" customWidth="1"/>
+    <col min="5" max="5" width="43.1796875" customWidth="1"/>
+    <col min="8" max="8" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" x14ac:dyDescent="0.4">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="27" t="s">
         <v>483</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="2" spans="1:3" ht="121.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="28"/>
+      <c r="C1" s="29"/>
+    </row>
+    <row r="2" spans="1:3" ht="121.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
         <v>484</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="30" t="s">
         <v>499</v>
       </c>
-      <c r="C2" s="15"/>
-    </row>
-    <row r="3" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="C2" s="30"/>
+    </row>
+    <row r="3" spans="1:3" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="31" t="s">
         <v>497</v>
       </c>
-      <c r="C3" s="18"/>
-    </row>
-    <row r="4" spans="1:3" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="C3" s="32"/>
+    </row>
+    <row r="4" spans="1:3" ht="63.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="C4" s="18"/>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="C4" s="32"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="13" t="s">
         <v>487</v>
       </c>
-      <c r="B5" s="20">
+      <c r="B5" s="33">
         <v>45933</v>
       </c>
-      <c r="C5" s="20"/>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-    </row>
-    <row r="7" spans="1:3" ht="24" x14ac:dyDescent="0.4">
-      <c r="A7" s="23" t="s">
+      <c r="C5" s="33"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="14"/>
+      <c r="B6" s="15"/>
+      <c r="C6" s="15"/>
+    </row>
+    <row r="7" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="34" t="s">
         <v>488</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="22"/>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="B7" s="35"/>
+      <c r="C7" s="15"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="16" t="s">
         <v>489</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="17" t="s">
         <v>490</v>
       </c>
-      <c r="C8" s="22"/>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="C8" s="15"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="16" t="s">
         <v>491</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="18" t="s">
         <v>492</v>
       </c>
-      <c r="C9" s="22"/>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="25" t="s">
+      <c r="C9" s="15"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="16" t="s">
         <v>493</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="18" t="s">
         <v>494</v>
       </c>
-      <c r="C10" s="22"/>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="28" t="s">
+      <c r="C10" s="15"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="18" t="s">
         <v>496</v>
       </c>
-      <c r="C11" s="22"/>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="22"/>
-    </row>
-    <row r="13" spans="1:3" ht="24" x14ac:dyDescent="0.4">
-      <c r="A13" s="30" t="s">
+      <c r="C11" s="15"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="C12" s="15"/>
+    </row>
+    <row r="13" spans="1:3" ht="23.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="25" t="s">
         <v>334</v>
       </c>
-      <c r="B13" s="30"/>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="31" t="s">
+      <c r="B13" s="25"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" s="20" t="s">
         <v>335</v>
       </c>
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="24" t="s">
         <v>336</v>
       </c>
-      <c r="C15" s="32"/>
-    </row>
-    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="B16" s="22" t="s">
         <v>338</v>
       </c>
-      <c r="C16" s="34"/>
-    </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="33" t="s">
+      <c r="C16" s="22"/>
+    </row>
+    <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A17" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="B17" s="35" t="s">
+      <c r="B17" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="C17" s="35"/>
-    </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
+      <c r="C17" s="26"/>
+    </row>
+    <row r="18" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A18" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="C18" s="34"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="27" t="s">
+      <c r="C18" s="22"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="26" t="s">
         <v>342</v>
       </c>
-      <c r="C19" s="35"/>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="27" t="s">
+      <c r="C19" s="26"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="C20" s="35"/>
-    </row>
-    <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="27" t="s">
+      <c r="C20" s="26"/>
+    </row>
+    <row r="21" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="34" t="s">
+      <c r="B21" s="22" t="s">
         <v>348</v>
       </c>
-      <c r="C21" s="34"/>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="27" t="s">
+      <c r="C21" s="22"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="22" t="s">
         <v>343</v>
       </c>
-      <c r="C22" s="34"/>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="27" t="s">
+      <c r="C22" s="22"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B23" s="22" t="s">
         <v>344</v>
       </c>
-      <c r="C23" s="34"/>
-    </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
+      <c r="C23" s="22"/>
+    </row>
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="22" t="s">
         <v>355</v>
       </c>
-      <c r="C24" s="34"/>
-    </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
+      <c r="C24" s="22"/>
+    </row>
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="B25" s="22" t="s">
         <v>354</v>
       </c>
-      <c r="C25" s="34"/>
-    </row>
-    <row r="26" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
+      <c r="C25" s="22"/>
+    </row>
+    <row r="26" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B26" s="34" t="s">
+      <c r="B26" s="22" t="s">
         <v>349</v>
       </c>
-      <c r="C26" s="34"/>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="27" t="s">
+      <c r="C26" s="22"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B27" s="36" t="s">
+      <c r="B27" s="23" t="s">
         <v>350</v>
       </c>
-      <c r="C27" s="36"/>
-    </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="27" t="s">
+      <c r="C27" s="23"/>
+    </row>
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="22" t="s">
         <v>351</v>
       </c>
-      <c r="C28" s="34"/>
-    </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="27" t="s">
+      <c r="C28" s="22"/>
+    </row>
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="22" t="s">
         <v>352</v>
       </c>
-      <c r="C29" s="34"/>
-    </row>
-    <row r="30" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="27" t="s">
+      <c r="C29" s="22"/>
+    </row>
+    <row r="30" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B30" s="34" t="s">
+      <c r="B30" s="22" t="s">
         <v>353</v>
       </c>
-      <c r="C30" s="34"/>
-    </row>
-    <row r="31" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="27" t="s">
+      <c r="C30" s="22"/>
+    </row>
+    <row r="31" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="C31" s="34"/>
-    </row>
-    <row r="32" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="27" t="s">
+      <c r="C31" s="22"/>
+    </row>
+    <row r="32" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="B32" s="22" t="s">
         <v>359</v>
       </c>
-      <c r="C32" s="34"/>
-    </row>
-    <row r="33" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="27" t="s">
+      <c r="C32" s="22"/>
+    </row>
+    <row r="33" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="22" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="34"/>
-    </row>
-    <row r="34" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="27" t="s">
+      <c r="C33" s="22"/>
+    </row>
+    <row r="34" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="B34" s="34" t="s">
+      <c r="B34" s="22" t="s">
         <v>361</v>
       </c>
-      <c r="C34" s="34"/>
-    </row>
-    <row r="35" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="27" t="s">
+      <c r="C34" s="22"/>
+    </row>
+    <row r="35" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="22" t="s">
         <v>362</v>
       </c>
-      <c r="C35" s="34"/>
-    </row>
-    <row r="36" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="27" t="s">
+      <c r="C35" s="22"/>
+    </row>
+    <row r="36" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B36" s="34" t="s">
+      <c r="B36" s="22" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="34"/>
-    </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="27" t="s">
+      <c r="C36" s="22"/>
+    </row>
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="22" t="s">
         <v>364</v>
       </c>
-      <c r="C37" s="34"/>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" s="27" t="s">
+      <c r="C37" s="22"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A38" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="22" t="s">
         <v>365</v>
       </c>
-      <c r="C38" s="34"/>
-    </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="27" t="s">
+      <c r="C38" s="22"/>
+    </row>
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="34" t="s">
+      <c r="B39" s="22" t="s">
         <v>366</v>
       </c>
-      <c r="C39" s="34"/>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" s="27" t="s">
+      <c r="C39" s="22"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A40" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="23" t="s">
         <v>346</v>
       </c>
-      <c r="C40" s="36"/>
+      <c r="C40" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="B24:C24"/>
@@ -3632,21 +3630,20 @@
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="B29:C29"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B40" location="Bibliography!A1" display="Number of reference available in Bibliography" xr:uid="{98E2F0E2-B32A-4040-9DF0-8E9D18DBB933}"/>
@@ -3659,12 +3656,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006B8963-F2B8-4E4A-8057-453E359A0D21}">
   <dimension ref="A1:Y224"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="25" max="25" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -3741,7 +3738,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -3815,7 +3812,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -3880,7 +3877,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3945,7 +3942,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -4013,7 +4010,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -4081,7 +4078,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -4152,7 +4149,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -4217,7 +4214,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -4288,7 +4285,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -4353,7 +4350,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -4421,7 +4418,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -4489,7 +4486,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -4557,7 +4554,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -4625,7 +4622,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4699,7 +4696,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>22</v>
       </c>
@@ -4764,7 +4761,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -4832,7 +4829,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -4900,7 +4897,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -4968,7 +4965,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -5036,7 +5033,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -5107,7 +5104,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>22</v>
       </c>
@@ -5175,7 +5172,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -5246,7 +5243,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -5311,7 +5308,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -5379,7 +5376,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -5450,7 +5447,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -5515,7 +5512,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -5580,7 +5577,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -5648,7 +5645,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>22</v>
       </c>
@@ -5719,7 +5716,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -5787,7 +5784,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -5855,7 +5852,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>22</v>
       </c>
@@ -5923,7 +5920,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>22</v>
       </c>
@@ -5991,7 +5988,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>22</v>
       </c>
@@ -6062,7 +6059,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>22</v>
       </c>
@@ -6130,7 +6127,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>22</v>
       </c>
@@ -6198,7 +6195,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>22</v>
       </c>
@@ -6269,7 +6266,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>22</v>
       </c>
@@ -6334,7 +6331,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>22</v>
       </c>
@@ -6402,7 +6399,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>22</v>
       </c>
@@ -6473,7 +6470,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>22</v>
       </c>
@@ -6541,7 +6538,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>22</v>
       </c>
@@ -6606,7 +6603,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>22</v>
       </c>
@@ -6674,7 +6671,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>22</v>
       </c>
@@ -6739,7 +6736,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>22</v>
       </c>
@@ -6807,7 +6804,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>22</v>
       </c>
@@ -6875,7 +6872,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>22</v>
       </c>
@@ -6943,7 +6940,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>22</v>
       </c>
@@ -7008,7 +7005,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>22</v>
       </c>
@@ -7076,7 +7073,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>22</v>
       </c>
@@ -7144,7 +7141,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>22</v>
       </c>
@@ -7212,7 +7209,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>22</v>
       </c>
@@ -7280,7 +7277,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -7351,7 +7348,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>22</v>
       </c>
@@ -7419,7 +7416,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>22</v>
       </c>
@@ -7487,7 +7484,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>22</v>
       </c>
@@ -7555,7 +7552,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>22</v>
       </c>
@@ -7626,7 +7623,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>22</v>
       </c>
@@ -7694,7 +7691,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>22</v>
       </c>
@@ -7762,7 +7759,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>22</v>
       </c>
@@ -7830,7 +7827,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>22</v>
       </c>
@@ -7898,7 +7895,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>22</v>
       </c>
@@ -7966,7 +7963,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>22</v>
       </c>
@@ -8034,7 +8031,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>22</v>
       </c>
@@ -8102,7 +8099,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>22</v>
       </c>
@@ -8167,7 +8164,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>22</v>
       </c>
@@ -8232,7 +8229,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>22</v>
       </c>
@@ -8297,7 +8294,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>22</v>
       </c>
@@ -8362,7 +8359,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>22</v>
       </c>
@@ -8430,7 +8427,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>22</v>
       </c>
@@ -8498,7 +8495,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>22</v>
       </c>
@@ -8566,7 +8563,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>22</v>
       </c>
@@ -8634,7 +8631,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>22</v>
       </c>
@@ -8702,7 +8699,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>22</v>
       </c>
@@ -8770,7 +8767,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>22</v>
       </c>
@@ -8838,7 +8835,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>22</v>
       </c>
@@ -8906,7 +8903,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>22</v>
       </c>
@@ -8974,7 +8971,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>22</v>
       </c>
@@ -9039,7 +9036,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>22</v>
       </c>
@@ -9107,7 +9104,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>22</v>
       </c>
@@ -9175,7 +9172,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>22</v>
       </c>
@@ -9243,7 +9240,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>22</v>
       </c>
@@ -9314,7 +9311,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>22</v>
       </c>
@@ -9385,7 +9382,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>22</v>
       </c>
@@ -9453,7 +9450,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>22</v>
       </c>
@@ -9521,7 +9518,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>22</v>
       </c>
@@ -9592,7 +9589,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>22</v>
       </c>
@@ -9660,7 +9657,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>22</v>
       </c>
@@ -9728,7 +9725,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>22</v>
       </c>
@@ -9796,7 +9793,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>22</v>
       </c>
@@ -9864,7 +9861,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>22</v>
       </c>
@@ -9932,7 +9929,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>22</v>
       </c>
@@ -10000,7 +9997,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>22</v>
       </c>
@@ -10071,7 +10068,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>22</v>
       </c>
@@ -10139,7 +10136,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>22</v>
       </c>
@@ -10207,7 +10204,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>22</v>
       </c>
@@ -10275,7 +10272,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>22</v>
       </c>
@@ -10340,7 +10337,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>22</v>
       </c>
@@ -10408,7 +10405,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>22</v>
       </c>
@@ -10476,7 +10473,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>22</v>
       </c>
@@ -10547,7 +10544,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>22</v>
       </c>
@@ -10615,7 +10612,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>22</v>
       </c>
@@ -10683,7 +10680,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>22</v>
       </c>
@@ -10751,7 +10748,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>22</v>
       </c>
@@ -10819,7 +10816,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>22</v>
       </c>
@@ -10887,7 +10884,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>22</v>
       </c>
@@ -10952,7 +10949,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>22</v>
       </c>
@@ -11020,7 +11017,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>22</v>
       </c>
@@ -11085,7 +11082,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>22</v>
       </c>
@@ -11153,7 +11150,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>22</v>
       </c>
@@ -11221,7 +11218,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>22</v>
       </c>
@@ -11289,7 +11286,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>22</v>
       </c>
@@ -11360,7 +11357,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>22</v>
       </c>
@@ -11431,7 +11428,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>22</v>
       </c>
@@ -11502,7 +11499,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>22</v>
       </c>
@@ -11570,7 +11567,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>22</v>
       </c>
@@ -11638,7 +11635,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>22</v>
       </c>
@@ -11703,7 +11700,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>22</v>
       </c>
@@ -11774,7 +11771,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>22</v>
       </c>
@@ -11839,7 +11836,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>22</v>
       </c>
@@ -11910,7 +11907,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>22</v>
       </c>
@@ -11975,7 +11972,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>22</v>
       </c>
@@ -12043,7 +12040,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>22</v>
       </c>
@@ -12111,7 +12108,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>22</v>
       </c>
@@ -12176,7 +12173,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>22</v>
       </c>
@@ -12244,7 +12241,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>22</v>
       </c>
@@ -12312,7 +12309,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>22</v>
       </c>
@@ -12377,7 +12374,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>22</v>
       </c>
@@ -12445,7 +12442,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>22</v>
       </c>
@@ -12513,7 +12510,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>22</v>
       </c>
@@ -12584,7 +12581,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>22</v>
       </c>
@@ -12655,7 +12652,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>22</v>
       </c>
@@ -12723,7 +12720,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>22</v>
       </c>
@@ -12788,7 +12785,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>22</v>
       </c>
@@ -12856,7 +12853,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>22</v>
       </c>
@@ -12924,7 +12921,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>22</v>
       </c>
@@ -12989,7 +12986,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>22</v>
       </c>
@@ -13060,7 +13057,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>22</v>
       </c>
@@ -13131,7 +13128,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>22</v>
       </c>
@@ -13196,7 +13193,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>22</v>
       </c>
@@ -13267,7 +13264,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>22</v>
       </c>
@@ -13335,7 +13332,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>22</v>
       </c>
@@ -13403,7 +13400,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>22</v>
       </c>
@@ -13474,7 +13471,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>22</v>
       </c>
@@ -13542,7 +13539,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>22</v>
       </c>
@@ -13607,7 +13604,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>22</v>
       </c>
@@ -13675,7 +13672,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>22</v>
       </c>
@@ -13743,7 +13740,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>22</v>
       </c>
@@ -13811,7 +13808,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>22</v>
       </c>
@@ -13882,7 +13879,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>22</v>
       </c>
@@ -13950,7 +13947,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>22</v>
       </c>
@@ -14018,7 +14015,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>22</v>
       </c>
@@ -14086,7 +14083,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>22</v>
       </c>
@@ -14157,7 +14154,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>22</v>
       </c>
@@ -14228,7 +14225,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>22</v>
       </c>
@@ -14296,7 +14293,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>22</v>
       </c>
@@ -14364,7 +14361,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>22</v>
       </c>
@@ -14432,7 +14429,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>22</v>
       </c>
@@ -14503,7 +14500,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>22</v>
       </c>
@@ -14571,7 +14568,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>22</v>
       </c>
@@ -14639,7 +14636,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>22</v>
       </c>
@@ -14707,7 +14704,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>22</v>
       </c>
@@ -14775,7 +14772,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>22</v>
       </c>
@@ -14846,7 +14843,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>22</v>
       </c>
@@ -14914,7 +14911,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>22</v>
       </c>
@@ -14982,7 +14979,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>22</v>
       </c>
@@ -15050,7 +15047,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>22</v>
       </c>
@@ -15118,7 +15115,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>22</v>
       </c>
@@ -15189,7 +15186,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>22</v>
       </c>
@@ -15257,7 +15254,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>22</v>
       </c>
@@ -15325,7 +15322,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>22</v>
       </c>
@@ -15390,7 +15387,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>22</v>
       </c>
@@ -15458,7 +15455,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>22</v>
       </c>
@@ -15523,7 +15520,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>22</v>
       </c>
@@ -15591,7 +15588,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>22</v>
       </c>
@@ -15656,7 +15653,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>22</v>
       </c>
@@ -15721,7 +15718,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>22</v>
       </c>
@@ -15789,7 +15786,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>22</v>
       </c>
@@ -15854,7 +15851,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>22</v>
       </c>
@@ -15919,7 +15916,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>22</v>
       </c>
@@ -15987,7 +15984,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>22</v>
       </c>
@@ -16055,7 +16052,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>22</v>
       </c>
@@ -16120,7 +16117,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>22</v>
       </c>
@@ -16188,7 +16185,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>22</v>
       </c>
@@ -16259,7 +16256,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>22</v>
       </c>
@@ -16330,7 +16327,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>22</v>
       </c>
@@ -16401,7 +16398,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>22</v>
       </c>
@@ -16469,7 +16466,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>22</v>
       </c>
@@ -16537,7 +16534,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>22</v>
       </c>
@@ -16602,7 +16599,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>22</v>
       </c>
@@ -16670,7 +16667,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>22</v>
       </c>
@@ -16735,7 +16732,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>22</v>
       </c>
@@ -16803,7 +16800,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>22</v>
       </c>
@@ -16868,7 +16865,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>22</v>
       </c>
@@ -16939,7 +16936,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>22</v>
       </c>
@@ -17004,7 +17001,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>22</v>
       </c>
@@ -17072,7 +17069,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>22</v>
       </c>
@@ -17140,7 +17137,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>22</v>
       </c>
@@ -17205,7 +17202,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>22</v>
       </c>
@@ -17273,7 +17270,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>22</v>
       </c>
@@ -17338,7 +17335,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>22</v>
       </c>
@@ -17406,7 +17403,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>22</v>
       </c>
@@ -17474,7 +17471,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>22</v>
       </c>
@@ -17542,7 +17539,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>22</v>
       </c>
@@ -17610,7 +17607,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>22</v>
       </c>
@@ -17678,7 +17675,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>22</v>
       </c>
@@ -17746,7 +17743,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>22</v>
       </c>
@@ -17814,7 +17811,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>22</v>
       </c>
@@ -17882,7 +17879,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>22</v>
       </c>
@@ -17950,7 +17947,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>22</v>
       </c>
@@ -18018,7 +18015,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>22</v>
       </c>
@@ -18086,7 +18083,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>22</v>
       </c>
@@ -18151,7 +18148,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>22</v>
       </c>
@@ -18216,7 +18213,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>22</v>
       </c>
@@ -18281,7 +18278,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>22</v>
       </c>
@@ -18346,7 +18343,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>22</v>
       </c>
@@ -18414,7 +18411,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>22</v>
       </c>
@@ -18482,7 +18479,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>22</v>
       </c>
@@ -18550,7 +18547,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>22</v>
       </c>
@@ -18615,7 +18612,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>22</v>
       </c>
@@ -18680,7 +18677,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>22</v>
       </c>
@@ -18745,7 +18742,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>22</v>
       </c>
@@ -18813,7 +18810,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>22</v>
       </c>
@@ -18887,21 +18884,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EBE54E0-4103-436B-869D-84F33731CF89}">
   <dimension ref="A1:B48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="11.26953125" customWidth="1"/>
     <col min="2" max="2" width="136" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="28.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="7" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="28.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:2" ht="28.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="8"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>436</v>
       </c>
@@ -18909,7 +18906,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="10">
         <v>1</v>
       </c>
@@ -18917,7 +18914,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="10">
         <v>2</v>
       </c>
@@ -18925,7 +18922,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="10">
         <v>3</v>
       </c>
@@ -18933,7 +18930,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="10">
         <v>4</v>
       </c>
@@ -18941,7 +18938,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="10">
         <v>5</v>
       </c>
@@ -18949,7 +18946,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="10">
         <v>6</v>
       </c>
@@ -18957,7 +18954,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="10">
         <v>7</v>
       </c>
@@ -18965,7 +18962,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="10">
         <v>8</v>
       </c>
@@ -18973,7 +18970,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="10">
         <v>9</v>
       </c>
@@ -18981,7 +18978,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="10">
         <v>10</v>
       </c>
@@ -18989,7 +18986,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="10">
         <v>11</v>
       </c>
@@ -18997,7 +18994,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="10">
         <v>12</v>
       </c>
@@ -19005,7 +19002,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>13</v>
       </c>
@@ -19013,7 +19010,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="10">
         <v>14</v>
       </c>
@@ -19021,7 +19018,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="10">
         <v>15</v>
       </c>
@@ -19029,7 +19026,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="10">
         <v>16</v>
       </c>
@@ -19037,7 +19034,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="10">
         <v>17</v>
       </c>
@@ -19045,7 +19042,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="10">
         <v>18</v>
       </c>
@@ -19053,7 +19050,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="10">
         <v>19</v>
       </c>
@@ -19061,7 +19058,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="10">
         <v>20</v>
       </c>
@@ -19069,7 +19066,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A24" s="10">
         <v>21</v>
       </c>
@@ -19077,7 +19074,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="10">
         <v>22</v>
       </c>
@@ -19085,7 +19082,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="10">
         <v>23</v>
       </c>
@@ -19093,7 +19090,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="10">
         <v>24</v>
       </c>
@@ -19101,7 +19098,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="10">
         <v>25</v>
       </c>
@@ -19109,7 +19106,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="10">
         <v>26</v>
       </c>
@@ -19117,7 +19114,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="10">
         <v>27</v>
       </c>
@@ -19125,7 +19122,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="10">
         <v>28</v>
       </c>
@@ -19133,7 +19130,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="10">
         <v>29</v>
       </c>
@@ -19141,7 +19138,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>30</v>
       </c>
@@ -19149,7 +19146,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>31</v>
       </c>
@@ -19157,7 +19154,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="10">
         <v>32</v>
       </c>
@@ -19165,7 +19162,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="10">
         <v>33</v>
       </c>
@@ -19173,7 +19170,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="10">
         <v>34</v>
       </c>
@@ -19181,7 +19178,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="10">
         <v>35</v>
       </c>
@@ -19189,7 +19186,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="10">
         <v>36</v>
       </c>
@@ -19197,7 +19194,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="10">
         <v>37</v>
       </c>
@@ -19205,7 +19202,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="10">
         <v>38</v>
       </c>
@@ -19213,7 +19210,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="10">
         <v>39</v>
       </c>
@@ -19221,7 +19218,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A43" s="10">
         <v>40</v>
       </c>
@@ -19229,7 +19226,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="10">
         <v>41</v>
       </c>
@@ -19237,7 +19234,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A45" s="10">
         <v>42</v>
       </c>
@@ -19245,7 +19242,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="10">
         <v>43</v>
       </c>
@@ -19253,7 +19250,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="10">
         <v>44</v>
       </c>
@@ -19261,7 +19258,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="10">
         <v>45</v>
       </c>
